--- a/artfynd/A 33659-2022 artfynd.xlsx
+++ b/artfynd/A 33659-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33659-2022 artfynd.xlsx
+++ b/artfynd/A 33659-2022 artfynd.xlsx
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83238415</v>
+        <v>110362053</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>6443</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tornslund, Ög</t>
+          <t>hagmarker S Fredriksberg, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538734.637880745</v>
+        <v>538533</v>
       </c>
       <c r="R2" t="n">
-        <v>6493620.691307731</v>
+        <v>6493690</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,29 +738,14 @@
           <t>Vånga</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>F525A1F3-3E5A-4A93-9FAC-9E71CF354A5F</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2001-02-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2001-02-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,69 +760,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110362053</v>
+        <v>83238415</v>
       </c>
       <c r="B3" t="n">
-        <v>76862</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6443</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>hagmarker S Fredriksberg, Ög</t>
+          <t>Tornslund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538532.8323719176</v>
+        <v>538735</v>
       </c>
       <c r="R3" t="n">
-        <v>6493690.130100307</v>
+        <v>6493621</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,24 +843,19 @@
           <t>Vånga</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>F525A1F3-3E5A-4A93-9FAC-9E71CF354A5F</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-02-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-02-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,17 +870,17 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Kenneth Claesson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Kenneth Claesson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+          <t>Trädportalen</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 33659-2022 artfynd.xlsx
+++ b/artfynd/A 33659-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110362053</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,8 +893,17 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83238415</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>